--- a/artfynd/A 46116-2025 artfynd.xlsx
+++ b/artfynd/A 46116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,6 +1489,113 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129745296</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alderbackberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601330</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6959016</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46116-2025 artfynd.xlsx
+++ b/artfynd/A 46116-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>129745296</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46116-2025 artfynd.xlsx
+++ b/artfynd/A 46116-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>129745296</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46116-2025 artfynd.xlsx
+++ b/artfynd/A 46116-2025 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>129745296</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46116-2025 artfynd.xlsx
+++ b/artfynd/A 46116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538858</v>
+        <v>112538868</v>
       </c>
       <c r="B2" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601341</v>
+        <v>601190</v>
       </c>
       <c r="R2" t="n">
-        <v>6959061</v>
+        <v>6958975</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112538860</v>
+        <v>112538862</v>
       </c>
       <c r="B3" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601370</v>
+        <v>601362</v>
       </c>
       <c r="R3" t="n">
-        <v>6958974</v>
+        <v>6958987</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112538859</v>
+        <v>112538864</v>
       </c>
       <c r="B4" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601425</v>
+        <v>601174</v>
       </c>
       <c r="R4" t="n">
-        <v>6959065</v>
+        <v>6959033</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112538863</v>
+        <v>112538861</v>
       </c>
       <c r="B5" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601224</v>
+        <v>601370</v>
       </c>
       <c r="R5" t="n">
-        <v>6959050</v>
+        <v>6958974</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112538857</v>
+        <v>112538863</v>
       </c>
       <c r="B6" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601315</v>
+        <v>601225</v>
       </c>
       <c r="R6" t="n">
-        <v>6959065</v>
+        <v>6959050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112538861</v>
+        <v>112538859</v>
       </c>
       <c r="B7" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601370</v>
+        <v>601425</v>
       </c>
       <c r="R7" t="n">
-        <v>6958974</v>
+        <v>6959065</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112538862</v>
+        <v>129745296</v>
       </c>
       <c r="B8" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1268,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-skälsjön, Mpd</t>
+          <t>Alderbackberget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601362</v>
+        <v>601330</v>
       </c>
       <c r="R8" t="n">
-        <v>6958987</v>
+        <v>6959016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1327,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,49 +1352,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112538864</v>
+        <v>112538857</v>
       </c>
       <c r="B9" t="n">
-        <v>89675</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601173</v>
+        <v>601315</v>
       </c>
       <c r="R9" t="n">
-        <v>6959034</v>
+        <v>6959065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,50 +1461,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129745296</v>
+        <v>112538858</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Alderbackberget, Mpd</t>
+          <t>Stor-skälsjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601330</v>
+        <v>601341</v>
       </c>
       <c r="R10" t="n">
-        <v>6959016</v>
+        <v>6959061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,17 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,15 +1546,403 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112538860</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>601370</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6958974</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112538865</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>601247</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6959021</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112538866</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>601323</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6958975</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112538867</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>601325</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6958960</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46116-2025 artfynd.xlsx
+++ b/artfynd/A 46116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538868</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538862</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538864</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538861</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538863</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745296</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538857</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538858</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538860</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538865</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538866</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,8 +2008,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>